--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J567"/>
+  <dimension ref="A1:J570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20854,6 +20854,114 @@
         <v>338.47</v>
       </c>
       <c r="J567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>314.78</v>
+      </c>
+      <c r="C568" t="n">
+        <v>309.46</v>
+      </c>
+      <c r="D568" t="n">
+        <v>315.48</v>
+      </c>
+      <c r="E568" t="n">
+        <v>323.11</v>
+      </c>
+      <c r="F568" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="G568" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="H568" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="I568" t="n">
+        <v>338.11</v>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="C569" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="D569" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="E569" t="n">
+        <v>322.64</v>
+      </c>
+      <c r="F569" t="n">
+        <v>326.72</v>
+      </c>
+      <c r="G569" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="H569" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="I569" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="C570" t="n">
+        <v>309.02</v>
+      </c>
+      <c r="D570" t="n">
+        <v>315.01</v>
+      </c>
+      <c r="E570" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="F570" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="G570" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="H570" t="n">
+        <v>343.47</v>
+      </c>
+      <c r="I570" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="J570" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20870,7 +20978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27763,6 +27871,46 @@
       </c>
       <c r="B689" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -27931,28 +28079,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02161854086006716</v>
+        <v>0.01969212144102312</v>
       </c>
       <c r="J2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003777881649560388</v>
+        <v>0.0003173139240756351</v>
       </c>
       <c r="M2" t="n">
-        <v>6.844363113273487</v>
+        <v>6.817265905829784</v>
       </c>
       <c r="N2" t="n">
-        <v>67.36374670457904</v>
+        <v>67.02534769165625</v>
       </c>
       <c r="O2" t="n">
-        <v>8.207542062309461</v>
+        <v>8.186900982157795</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0921329427915</v>
+        <v>316.1125670934181</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28009,28 +28157,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2266704366824772</v>
+        <v>0.2231338846991464</v>
       </c>
       <c r="J3" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K3" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03249681329271592</v>
+        <v>0.03188256754062357</v>
       </c>
       <c r="M3" t="n">
-        <v>7.419123983177918</v>
+        <v>7.399396334760509</v>
       </c>
       <c r="N3" t="n">
-        <v>83.32730206532294</v>
+        <v>82.94435398869904</v>
       </c>
       <c r="O3" t="n">
-        <v>9.128378939621369</v>
+        <v>9.107379095475221</v>
       </c>
       <c r="P3" t="n">
-        <v>306.0798121713619</v>
+        <v>306.1173299437102</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28087,28 +28235,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1203395620865076</v>
+        <v>0.1158433517376086</v>
       </c>
       <c r="J4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007723593721566169</v>
+        <v>0.007243733419557197</v>
       </c>
       <c r="M4" t="n">
-        <v>8.288613348811682</v>
+        <v>8.267304152905675</v>
       </c>
       <c r="N4" t="n">
-        <v>101.3481969998957</v>
+        <v>100.9028495953869</v>
       </c>
       <c r="O4" t="n">
-        <v>10.06718416439749</v>
+        <v>10.04504104498269</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1165000820757</v>
+        <v>316.1641983376817</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28165,28 +28313,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09364338436465375</v>
+        <v>0.09148594166333217</v>
       </c>
       <c r="J5" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K5" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006647938967215494</v>
+        <v>0.006423971612883994</v>
       </c>
       <c r="M5" t="n">
-        <v>7.032782705746448</v>
+        <v>7.006324044607204</v>
       </c>
       <c r="N5" t="n">
-        <v>71.37667368061807</v>
+        <v>71.02107491580634</v>
       </c>
       <c r="O5" t="n">
-        <v>8.448471677209913</v>
+        <v>8.427400246565149</v>
       </c>
       <c r="P5" t="n">
-        <v>322.4496655001569</v>
+        <v>322.4725519482071</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28243,28 +28391,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08729931666182142</v>
+        <v>0.08389223284930752</v>
       </c>
       <c r="J6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0106290350201953</v>
+        <v>0.009931859228963891</v>
       </c>
       <c r="M6" t="n">
-        <v>4.953985802636006</v>
+        <v>4.944251734778002</v>
       </c>
       <c r="N6" t="n">
-        <v>38.64318736824723</v>
+        <v>38.49098824341017</v>
       </c>
       <c r="O6" t="n">
-        <v>6.216364481612001</v>
+        <v>6.204110592454826</v>
       </c>
       <c r="P6" t="n">
-        <v>327.2314192971503</v>
+        <v>327.2675644620688</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28321,28 +28469,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1971620648280633</v>
+        <v>0.196332104162805</v>
       </c>
       <c r="J7" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K7" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09611648866081912</v>
+        <v>0.09644875393105234</v>
       </c>
       <c r="M7" t="n">
-        <v>3.526435845847135</v>
+        <v>3.512033928013389</v>
       </c>
       <c r="N7" t="n">
-        <v>19.91348228204844</v>
+        <v>19.81161293002032</v>
       </c>
       <c r="O7" t="n">
-        <v>4.46245249633522</v>
+        <v>4.451023806948275</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5131730678401</v>
+        <v>324.5219784407598</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28399,28 +28547,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01613109373671425</v>
+        <v>0.02088138418851833</v>
       </c>
       <c r="J8" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K8" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00088892417894193</v>
+        <v>0.001497536085592444</v>
       </c>
       <c r="M8" t="n">
-        <v>2.872228517150086</v>
+        <v>2.879703496351051</v>
       </c>
       <c r="N8" t="n">
-        <v>15.93171809073267</v>
+        <v>15.95039477979464</v>
       </c>
       <c r="O8" t="n">
-        <v>3.991455635571147</v>
+        <v>3.993794533998293</v>
       </c>
       <c r="P8" t="n">
-        <v>339.6321217234748</v>
+        <v>339.5817359687462</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28477,28 +28625,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.031725580728322</v>
+        <v>0.02731367339637169</v>
       </c>
       <c r="J9" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K9" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002180459545357061</v>
+        <v>0.001631666654035913</v>
       </c>
       <c r="M9" t="n">
-        <v>3.851794759297135</v>
+        <v>3.850196958797403</v>
       </c>
       <c r="N9" t="n">
-        <v>25.09048527843704</v>
+        <v>25.04382195333944</v>
       </c>
       <c r="O9" t="n">
-        <v>5.009040355041776</v>
+        <v>5.004380276651589</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1593420077115</v>
+        <v>341.2061448359144</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28536,7 +28684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J567"/>
+  <dimension ref="A1:J570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58023,6 +58171,162 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-36.9617070886692,175.8431237426074</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-36.96242257833342,175.84322798699316</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-36.963133105178215,175.84346092438847</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-36.96383694222005,175.84378527029443</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-36.96451917158442,175.84414171293687</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-36.965170806875385,175.84452213918695</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-36.96578524866566,175.84500679373136</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-36.96647442346816,175.84528755649876</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-36.96170741295154,175.84312176302535</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-36.96242486633448,175.84321401981404</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-36.963133921773,175.8434567821731</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-36.96383829966031,175.84378027320034</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-36.96451875250655,175.84414295455983</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-36.96517087720799,175.84452193250402</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-36.96578905132429,175.84499563525182</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-36.96647579729303,175.84528377248608</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-36.96170615185336,175.8431294613999</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-36.96242337102689,175.84322314797058</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-36.96313411517701,175.84345580112205</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-36.96383682669322,175.84378569557904</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-36.96452137174305,175.84413519441617</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-36.96517182669796,175.84451914228447</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-36.965792255415515,175.84498623319868</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-36.966474869033,175.84528632925142</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J570"/>
+  <dimension ref="A1:J575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20962,6 +20962,186 @@
         <v>337.99</v>
       </c>
       <c r="J570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>317.97</v>
+      </c>
+      <c r="C571" t="n">
+        <v>311.88</v>
+      </c>
+      <c r="D571" t="n">
+        <v>317.73</v>
+      </c>
+      <c r="E571" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="F571" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="G571" t="n">
+        <v>330.54</v>
+      </c>
+      <c r="H571" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="I571" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>319.36</v>
+      </c>
+      <c r="C572" t="n">
+        <v>313.09</v>
+      </c>
+      <c r="D572" t="n">
+        <v>318.96</v>
+      </c>
+      <c r="E572" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="F572" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="G572" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="H572" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="I572" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:59:33+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="C573" t="n">
+        <v>310.8</v>
+      </c>
+      <c r="D573" t="n">
+        <v>317.53</v>
+      </c>
+      <c r="E573" t="n">
+        <v>325.21</v>
+      </c>
+      <c r="F573" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="G573" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="H573" t="n">
+        <v>343</v>
+      </c>
+      <c r="I573" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="C574" t="n">
+        <v>310.8</v>
+      </c>
+      <c r="D574" t="n">
+        <v>315.21</v>
+      </c>
+      <c r="E574" t="n">
+        <v>324.52</v>
+      </c>
+      <c r="F574" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="G574" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="H574" t="n">
+        <v>343</v>
+      </c>
+      <c r="I574" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="C575" t="n">
+        <v>310.88</v>
+      </c>
+      <c r="D575" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="E575" t="n">
+        <v>324.66</v>
+      </c>
+      <c r="F575" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="G575" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="H575" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="I575" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="J575" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20978,7 +21158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27911,6 +28091,56 @@
       </c>
       <c r="B693" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-08-14 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -28079,28 +28309,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01969212144102312</v>
+        <v>0.02222297157978808</v>
       </c>
       <c r="J2" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K2" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003173139240756351</v>
+        <v>0.000412308556026586</v>
       </c>
       <c r="M2" t="n">
-        <v>6.817265905829784</v>
+        <v>6.770431939440375</v>
       </c>
       <c r="N2" t="n">
-        <v>67.02534769165625</v>
+        <v>66.46254985738777</v>
       </c>
       <c r="O2" t="n">
-        <v>8.186900982157795</v>
+        <v>8.152456676204283</v>
       </c>
       <c r="P2" t="n">
-        <v>316.1125670934181</v>
+        <v>316.0856046519166</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28157,28 +28387,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2231338846991464</v>
+        <v>0.2220189677833872</v>
       </c>
       <c r="J3" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K3" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03188256754062357</v>
+        <v>0.03220300115511499</v>
       </c>
       <c r="M3" t="n">
-        <v>7.399396334760509</v>
+        <v>7.344401079398698</v>
       </c>
       <c r="N3" t="n">
-        <v>82.94435398869904</v>
+        <v>82.23226764971639</v>
       </c>
       <c r="O3" t="n">
-        <v>9.107379095475221</v>
+        <v>9.068200904794534</v>
       </c>
       <c r="P3" t="n">
-        <v>306.1173299437102</v>
+        <v>306.1292247626099</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28235,28 +28465,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1158433517376086</v>
+        <v>0.1116107781028016</v>
       </c>
       <c r="J4" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K4" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007243733419557197</v>
+        <v>0.006861152791430292</v>
       </c>
       <c r="M4" t="n">
-        <v>8.267304152905675</v>
+        <v>8.216025051102251</v>
       </c>
       <c r="N4" t="n">
-        <v>100.9028495953869</v>
+        <v>100.0919927237264</v>
       </c>
       <c r="O4" t="n">
-        <v>10.04504104498269</v>
+        <v>10.00459857883995</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1641983376817</v>
+        <v>316.209332157372</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28313,28 +28543,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09148594166333217</v>
+        <v>0.09215965022717282</v>
       </c>
       <c r="J5" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K5" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006423971612883994</v>
+        <v>0.006651669957309814</v>
       </c>
       <c r="M5" t="n">
-        <v>7.006324044607204</v>
+        <v>6.950923436036034</v>
       </c>
       <c r="N5" t="n">
-        <v>71.02107491580634</v>
+        <v>70.40875973200373</v>
       </c>
       <c r="O5" t="n">
-        <v>8.427400246565149</v>
+        <v>8.390992773921553</v>
       </c>
       <c r="P5" t="n">
-        <v>322.4725519482071</v>
+        <v>322.4653843409384</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28391,28 +28621,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08389223284930752</v>
+        <v>0.08191655399958249</v>
       </c>
       <c r="J6" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K6" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009931859228963891</v>
+        <v>0.009665110503088159</v>
       </c>
       <c r="M6" t="n">
-        <v>4.944251734778002</v>
+        <v>4.910510921599616</v>
       </c>
       <c r="N6" t="n">
-        <v>38.49098824341017</v>
+        <v>38.16741872610908</v>
       </c>
       <c r="O6" t="n">
-        <v>6.204110592454826</v>
+        <v>6.177978530725813</v>
       </c>
       <c r="P6" t="n">
-        <v>327.2675644620688</v>
+        <v>327.288618145752</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28469,28 +28699,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.196332104162805</v>
+        <v>0.1972622814578095</v>
       </c>
       <c r="J7" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K7" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09644875393105234</v>
+        <v>0.09906260524167598</v>
       </c>
       <c r="M7" t="n">
-        <v>3.512033928013389</v>
+        <v>3.486606523809022</v>
       </c>
       <c r="N7" t="n">
-        <v>19.81161293002032</v>
+        <v>19.6447793983992</v>
       </c>
       <c r="O7" t="n">
-        <v>4.451023806948275</v>
+        <v>4.432243156506557</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5219784407598</v>
+        <v>324.5120762035249</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28547,28 +28777,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02088138418851833</v>
+        <v>0.02639470556452919</v>
       </c>
       <c r="J8" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K8" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001497536085592444</v>
+        <v>0.002426935500699723</v>
       </c>
       <c r="M8" t="n">
-        <v>2.879703496351051</v>
+        <v>2.88148597965651</v>
       </c>
       <c r="N8" t="n">
-        <v>15.95039477979464</v>
+        <v>15.89623622983796</v>
       </c>
       <c r="O8" t="n">
-        <v>3.993794533998293</v>
+        <v>3.987008431122006</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5817359687462</v>
+        <v>339.5229918711107</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28625,28 +28855,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02731367339637169</v>
+        <v>0.02051424045334243</v>
       </c>
       <c r="J9" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K9" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001631666654035913</v>
+        <v>0.0009354051449724787</v>
       </c>
       <c r="M9" t="n">
-        <v>3.850196958797403</v>
+        <v>3.845545158910122</v>
       </c>
       <c r="N9" t="n">
-        <v>25.04382195333944</v>
+        <v>24.9504787040718</v>
       </c>
       <c r="O9" t="n">
-        <v>5.004380276651589</v>
+        <v>4.995045415616539</v>
       </c>
       <c r="P9" t="n">
-        <v>341.2061448359144</v>
+        <v>341.278608877765</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28684,7 +28914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J570"/>
+  <dimension ref="A1:J575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58327,6 +58557,266 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-36.96170134166008,175.84315882519743</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-36.96241821851596,175.84325460161537</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-36.963128270074606,175.84348545066177</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-36.96383003948883,175.84381068104662</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-36.964514107725954,175.84415671587988</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-36.96516584842677,175.8445367103324</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-36.96579070618468,175.84499077924644</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-36.966475017554615,175.84528592016895</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-36.96169883747425,175.8431741119668</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-36.96241603860503,175.8432679089252</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-36.96312562688255,175.84349885835638</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-36.96382668920735,175.84382301429693</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-36.96451110433319,175.84416561417615</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-36.965162964789194,175.84454518433094</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-36.965790565345515,175.8449911925235</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-36.96647356946887,175.8452899087228</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:59:33+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-36.96170170197445,175.8431566256622</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-36.96242016422034,175.84324272401582</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-36.963128699861805,175.84348327054872</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-36.963830877059,175.84380759773384</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-36.964513514032085,175.84415847484547</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-36.96516655175291,175.84453464350338</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-36.96579391027554,175.84498137719288</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-36.96647356946887,175.8452899087228</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-36.96170170197445,175.8431566256622</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-36.96242016422034,175.84324272401582</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-36.96313368539031,175.84345798123542</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-36.96383286989809,175.8438002615756</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-36.964514072802785,175.84415681934843</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-36.96516876723007,175.8445281329917</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-36.96579391027554,175.84498137719288</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-36.96647356946887,175.8452899087228</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-36.96170224244589,175.84315332635927</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-36.96242002009412,175.84324360383803</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-36.963133986241,175.8434564551561</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-36.96383246555396,175.8438017500715</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-36.96451141864177,175.8441646829591</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-36.965168907895276,175.8445277196259</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-36.96579609328209,175.84497497139765</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-36.966476354249025,175.84528223842685</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0186/nzd0186.xlsx
+++ b/data/nzd0186/nzd0186.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J575"/>
+  <dimension ref="A1:J579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21049,7 +21049,7 @@
         <v>317.77</v>
       </c>
       <c r="C573" t="n">
-        <v>310.8</v>
+        <v>313.09</v>
       </c>
       <c r="D573" t="n">
         <v>317.53</v>
@@ -21085,7 +21085,7 @@
         <v>317.77</v>
       </c>
       <c r="C574" t="n">
-        <v>310.8</v>
+        <v>313.09</v>
       </c>
       <c r="D574" t="n">
         <v>315.21</v>
@@ -21121,7 +21121,7 @@
         <v>317.47</v>
       </c>
       <c r="C575" t="n">
-        <v>310.88</v>
+        <v>313.18</v>
       </c>
       <c r="D575" t="n">
         <v>315.07</v>
@@ -21142,6 +21142,150 @@
         <v>337.59</v>
       </c>
       <c r="J575" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>318.71</v>
+      </c>
+      <c r="C576" t="n">
+        <v>313.18</v>
+      </c>
+      <c r="D576" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="E576" t="n">
+        <v>324.66</v>
+      </c>
+      <c r="F576" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="G576" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="H576" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="I576" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>319.37</v>
+      </c>
+      <c r="C577" t="n">
+        <v>314.27</v>
+      </c>
+      <c r="D577" t="n">
+        <v>315.31</v>
+      </c>
+      <c r="E577" t="n">
+        <v>324.85</v>
+      </c>
+      <c r="F577" t="n">
+        <v>328.62</v>
+      </c>
+      <c r="G577" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="H577" t="n">
+        <v>342.06</v>
+      </c>
+      <c r="I577" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>320.84</v>
+      </c>
+      <c r="C578" t="n">
+        <v>315.12</v>
+      </c>
+      <c r="D578" t="n">
+        <v>317.21</v>
+      </c>
+      <c r="E578" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="F578" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="G578" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="H578" t="n">
+        <v>342.57</v>
+      </c>
+      <c r="I578" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="C579" t="n">
+        <v>315.29</v>
+      </c>
+      <c r="D579" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="E579" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="F579" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="G579" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="H579" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="I579" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="J579" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21158,7 +21302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B698"/>
+  <dimension ref="A1:B703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28141,6 +28285,56 @@
       </c>
       <c r="B698" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -28309,28 +28503,28 @@
         <v>0.0593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02222297157978808</v>
+        <v>0.02684934358490102</v>
       </c>
       <c r="J2" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K2" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000412308556026586</v>
+        <v>0.0006107076904432462</v>
       </c>
       <c r="M2" t="n">
-        <v>6.770431939440375</v>
+        <v>6.746274248995469</v>
       </c>
       <c r="N2" t="n">
-        <v>66.46254985738777</v>
+        <v>66.08339054954278</v>
       </c>
       <c r="O2" t="n">
-        <v>8.152456676204283</v>
+        <v>8.129169118030623</v>
       </c>
       <c r="P2" t="n">
-        <v>316.0856046519166</v>
+        <v>316.0361427782108</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28387,28 +28581,28 @@
         <v>0.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2220189677833872</v>
+        <v>0.2276999452150638</v>
       </c>
       <c r="J3" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K3" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03220300115511499</v>
+        <v>0.03432841322381952</v>
       </c>
       <c r="M3" t="n">
-        <v>7.344401079398698</v>
+        <v>7.303897495583234</v>
       </c>
       <c r="N3" t="n">
-        <v>82.23226764971639</v>
+        <v>81.7005998980483</v>
       </c>
       <c r="O3" t="n">
-        <v>9.068200904794534</v>
+        <v>9.038838415308037</v>
       </c>
       <c r="P3" t="n">
-        <v>306.1292247626099</v>
+        <v>306.068551008563</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28465,28 +28659,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1116107781028016</v>
+        <v>0.1075003416634813</v>
       </c>
       <c r="J4" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K4" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006861152791430292</v>
+        <v>0.006466223831175899</v>
       </c>
       <c r="M4" t="n">
-        <v>8.216025051102251</v>
+        <v>8.17908038215424</v>
       </c>
       <c r="N4" t="n">
-        <v>100.0919927237264</v>
+        <v>99.4661390786672</v>
       </c>
       <c r="O4" t="n">
-        <v>10.00459857883995</v>
+        <v>9.973271232582977</v>
       </c>
       <c r="P4" t="n">
-        <v>316.209332157372</v>
+        <v>316.2532506965933</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28543,28 +28737,28 @@
         <v>0.0631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09215965022717282</v>
+        <v>0.09311930369390728</v>
       </c>
       <c r="J5" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K5" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006651669957309814</v>
+        <v>0.006898151199654645</v>
       </c>
       <c r="M5" t="n">
-        <v>6.950923436036034</v>
+        <v>6.908789636099512</v>
       </c>
       <c r="N5" t="n">
-        <v>70.40875973200373</v>
+        <v>69.93010655235796</v>
       </c>
       <c r="O5" t="n">
-        <v>8.390992773921553</v>
+        <v>8.362422289764966</v>
       </c>
       <c r="P5" t="n">
-        <v>322.4653843409384</v>
+        <v>322.4551149923661</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28621,28 +28815,28 @@
         <v>0.0548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08191655399958249</v>
+        <v>0.08231594532767683</v>
       </c>
       <c r="J6" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K6" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009665110503088159</v>
+        <v>0.00991271935557092</v>
       </c>
       <c r="M6" t="n">
-        <v>4.910510921599616</v>
+        <v>4.883923792977358</v>
       </c>
       <c r="N6" t="n">
-        <v>38.16741872610908</v>
+        <v>37.91161451838952</v>
       </c>
       <c r="O6" t="n">
-        <v>6.177978530725813</v>
+        <v>6.157240820236733</v>
       </c>
       <c r="P6" t="n">
-        <v>327.288618145752</v>
+        <v>327.2843359288429</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28699,28 +28893,28 @@
         <v>0.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1972622814578095</v>
+        <v>0.1972479983147345</v>
       </c>
       <c r="J7" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K7" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09906260524167598</v>
+        <v>0.1004898340033878</v>
       </c>
       <c r="M7" t="n">
-        <v>3.486606523809022</v>
+        <v>3.463026748386688</v>
       </c>
       <c r="N7" t="n">
-        <v>19.6447793983992</v>
+        <v>19.50890193713229</v>
       </c>
       <c r="O7" t="n">
-        <v>4.432243156506557</v>
+        <v>4.416888264053359</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5120762035249</v>
+        <v>324.5122278661451</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28777,28 +28971,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02639470556452919</v>
+        <v>0.02925176345505991</v>
       </c>
       <c r="J8" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K8" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002426935500699723</v>
+        <v>0.003021687949519847</v>
       </c>
       <c r="M8" t="n">
-        <v>2.88148597965651</v>
+        <v>2.875524922270441</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89623622983796</v>
+        <v>15.81480616107208</v>
       </c>
       <c r="O8" t="n">
-        <v>3.987008431122006</v>
+        <v>3.976783393783483</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5229918711107</v>
+        <v>339.4924554464114</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28855,28 +29049,28 @@
         <v>0.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02051424045334243</v>
+        <v>0.01494243922884447</v>
       </c>
       <c r="J9" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K9" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009354051449724787</v>
+        <v>0.0005023424047816416</v>
       </c>
       <c r="M9" t="n">
-        <v>3.845545158910122</v>
+        <v>3.842979541092723</v>
       </c>
       <c r="N9" t="n">
-        <v>24.9504787040718</v>
+        <v>24.88562807121399</v>
       </c>
       <c r="O9" t="n">
-        <v>4.995045415616539</v>
+        <v>4.988549696175632</v>
       </c>
       <c r="P9" t="n">
-        <v>341.278608877765</v>
+        <v>341.3381593590217</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28914,7 +29108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J575"/>
+  <dimension ref="A1:J579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58674,7 +58868,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>-36.96242016422034,175.84324272401582</t>
+          <t>-36.96241603860503,175.8432679089252</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -58726,7 +58920,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>-36.96242016422034,175.84324272401582</t>
+          <t>-36.96241603860503,175.8432679089252</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -58778,7 +58972,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>-36.96242002009412,175.84324360383803</t>
+          <t>-36.96241587646283,175.84326889872509</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -58812,6 +59006,214 @@
         </is>
       </c>
       <c r="J575" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-36.96170000849664,175.84316696347767</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-36.96241587646283,175.84326889872509</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-36.963133986241,175.8434564551561</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-36.96383246555396,175.8438017500715</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-36.96451141864177,175.8441646829591</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-36.965168907895276,175.8445277196259</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-36.96579609328209,175.84497497139765</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-36.966476354249025,175.84528223842685</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-36.961698819458526,175.84317422194354</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-36.96241391274007,175.84328088630093</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-36.963133470496956,175.84345907129213</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-36.96383191680119,175.84380377017308</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-36.96451211710524,175.84416261358794</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-36.965168450733366,175.8445290630648</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-36.965797219995004,175.84497166518062</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-36.96647579729303,175.84528377248608</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-36.961696171144766,175.84319038852573</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-36.962412381395794,175.84329023441</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-36.96312938752122,175.8434797823678</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-36.96382758454131,175.84381971834222</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-36.964504364158714,175.8441855836057</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-36.96516788807251,175.84453071652814</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-36.96579542429624,175.84497693446397</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-36.96647475764179,175.84528663606324</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-36.96169579281407,175.84319269803737</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-36.96241207512686,175.8432921040318</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-36.96312876432988,175.84348294353177</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-36.963826631443865,175.84382322693918</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-36.964504364158714,175.8441855836057</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-36.965168310068144,175.84452947643067</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-36.96579704394612,175.84497218177705</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-36.96647475764179,175.84528663606324</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
